--- a/examples/台账_2026-08.xlsx
+++ b/examples/台账_2026-08.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>高原州社区遇袭，一名地方议员称袭击致 23 人死亡、另有 1 人送医后不治，共 25 人</t>
+          <t>一名身份不明女性携伪装成礼盒的简易爆炸装置，欲进入餐厅内私人宴会，入口被保安拦下后于露台引爆。宴会据信为俄空天军总司令柴科生日聚会，被视为针对俄军高层的暗杀企图。</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>俄罗斯</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -570,47 +570,43 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>高原州（Plateau）</t>
+          <t>莫斯科 昆德林斯卡亚广场 Balzi Rossi 餐厅</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>枪击</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>枪支</t>
-        </is>
-      </c>
+          <t>自杀式爆炸 / 定点暗杀</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>不明武装分子（农民与牧民冲突背景）</t>
+          <t>身份不明女性袭击者（无人宣称）</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>未识别</t>
+          <t>身份不明女性袭击者（无人宣称）</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/africa/least-25-killed-attack-nigerias-plateau-amid-reprisal-fears-2026-08-18/</t>
+          <t>https://www.reuters.com/world/three-killed-15-injured-moscow-explosion-tass-says-2026-08-01/</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>示例组</t>
+          <t>第七组</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -630,24 +626,24 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>P3 平民社区无差别暴力；反证 N1/N2 未成立</t>
+          <t>P3 命中；反证已逐条排查</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>[证据] Lemun Le'an Iliya, a councillor representing the area, said 23 people were killed in the attack and another victim later died in hospital.</t>
+          <t>[判据]P3 目标为军警人员（宴会被视为针对俄军高层的定点袭击）；反证 N1/N2/N3 均不成立 [证据]Aug 1 (Reuters) - Three people were killed and 15 injured in an explosion near a cafe in central Moscow, TASS  [日期]URL 内嵌 2026-08-01；原文首句『Aug 1 (Reuters)』；维基条目《2026 Moscow res</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>胡塞武装袭击也门政府军营地，至少 30 名政府军士兵死亡</t>
+          <t>一辆载满炸药的卡车在警察局旁爆炸。哥政府明确归因于国内最大在野武装『民族解放军』（ELN）。事发于当选总统就职前 6 天。</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>也门</t>
+          <t>哥伦比亚</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -657,47 +653,43 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>马里布省与哈德拉毛省</t>
+          <t>北桑坦德省 库库塔市（Cúcuta）警察局旁</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>袭击</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>不明/其他</t>
-        </is>
-      </c>
+          <t>卡车炸弹（VBIED）</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>胡塞武装</t>
+          <t>民族解放军（ELN）</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>胡塞武装（安萨鲁拉）</t>
+          <t>民族解放军（ELN）</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/least-30-yemeni-government-troops-killed-houthi-attacks-sources-say-2026-08-06/</t>
+          <t>https://www.france24.com/en/live-news/20260801-11-injured-in-colombia-bombing-days-before-presidential-inauguration</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>示例组</t>
+          <t>第七组</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -717,24 +709,24 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>P1 组织公开宣称；反证 N4 需核是否已交战状态</t>
+          <t>P3 命中；反证已逐条排查</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>[证据] Houthi attacks kill at least 30 Yemeni government troops ... military camps, weapons depots and vehicles were destroyed.</t>
+          <t>[判据]P3 目标为警察局（国家象征）；ELN 为政府明确归因的非国家武装；受害者 14 人受伤≥3 [证据]A truck bomb exploded Saturday near a Colombian police station not far from the Venezuelan border, wounding 14 [日期]URL 内嵌 20260801；原文『Issued on: 01/08/2026』；CBS 报道称『Saturday』（</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>反政府武装袭击伊图里省两处村庄，Mabakuha 村至少 10 人死亡、Amani 村寻回 11 具遗体，合计升至 21 人</t>
+          <t>武装分子深夜突袭村庄，开枪扫射并纵火，随后劫走妇女儿童与牲畜。一户六口被烧死在屋内。</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>刚果（金）</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -744,72 +736,1230 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>索科托州 拉金盖村（Lajinge）</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>武装袭击 / 纵火 / 绑架</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>不明武装匪帮（当地称 bandits）</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>不明武装匪帮（当地称 bandits）</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/world/africa/gunmen-kill-12-abduct-women-children-nigerian-village-2026-08-02/</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 目标为平民村庄；有杀人+纵火，非「以索赎为唯一目的」，故不落 N2 [证据]Armed men killed at least 12 people and abducted women and children during a night attack on a village in Nige [日期]URL 内嵌 2026-08-02；原文首句『MAIDUGURI, Aug 2 (Reuters)』；文中称袭击发生于周</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>一名自杀式袭击者在警察局外人群聚集处引爆炸弹，当时正有民众在警察局前抗议近期恐怖主义浪潮。袭击者单独行动。</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>巴基斯坦</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>开伯尔-普什图省 斯瓦特 卡巴尔（Kabal）警察局外</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>自杀式爆炸</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>未宣称（疑似 TTP 系）</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>未宣称（疑似 TTP 系）</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aa.com.tr/en/asia-pacific/5-killed-several-injured-in-suspected-suicide-bombing-in-northwestern-pakistan/4016402</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 目标为警察局+平民聚集；自杀式爆炸，非反恐战果；N1/N2 不成立 [证据]The death toll from a suicide bombing outside a police station in northwestern Pakistan on Sunday evening clim [日期]原文页头『02 August 2026•Update: 02 August 2026』；同日 Reuters 报道称『A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>分离主义武装袭击公路施工营地，杀害受雇于 PT SHJ 的筑路工人。军方言称袭击者指工人为『雅加达间谍』。</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>巴布亚高地省 托利卡拉县（Tolikara）</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>武装袭击 / 枪击</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>巴布亚分离主义武装（印尼官方称 KKB）</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>巴布亚分离主义武装（印尼官方称 KKB）</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://en.antaranews.com/news/425187/five-workers-killed-by-insurgents-in-highland-papua-manhunt-ongoing</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 目标为受雇筑路工人（民用设施劳动者）；分离武装 KKB 非国家主体 [缺口]受伤数原文未给，按口径记 0，不等于「无人受伤」 [证据]Jayapura (ANTARA) - Five workers were killed by armed insurgents in a Sunday attack in Tolikara District, High [日期]原文页头『August 3, 2026 12:42 GMT+700』；正文『a Sunday attack』，2026-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>一辆小巴车内被安置炸弹后爆炸。贾拉马纳为德鲁兹与基督徒聚居镇。无组织宣称。</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>叙利亚</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>大马士革郊区 贾拉马纳（Jaramana）</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>车载简易爆炸装置（IED）</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>未宣称</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>未宣称</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.france24.com/en/live-news/20260806-2-killed-13-wounded-in-bus-blast-near-syrian-capital-state-media</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 民用小巴乘客；无宣称但主体非国家力量，N1/N2/N3 均无线索 [证据]Damascus (AFP) – At least two people were killed and 13 wounded after a bomb planted on a minibus exploded on  [日期]URL 内嵌 20260806；原文『Issued on: 06/08/2026 - 21:11』；正文称爆炸发生于『T</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>疑似『博科圣地』武装分子夜间入村袭击，杀害居民、洗劫商铺与牲畜并破坏集市。</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>喀麦隆</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>极北省 马约-萨瓦 坎加莱里村（Kangaleri）</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>武装袭击</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>博科圣地（Boko Haram，疑似）</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>博科圣地（Boko Haram，疑似）</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://newsaf.cgtn.com/news/2026-08-09/Eight-killed-in-suspected-Boko-Haram-raid-in-Cameroon-1Ps59Z25B3q/p.html</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 平民村民与集市；疑为博科圣地（联合国名单组织），主体仅「疑似」不影响判据命中 [证据]At least eight people were killed and another injured in an overnight attack by suspected Boko Haram fighters  [日期]URL 内嵌 2026-08-09（报道日）；正文『local sources said Saturday』、袭击发生于</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>约 240 名骑摩托车的武装匪帮与警方交火，10 名警员殉职、2 名警员受伤，2 名平民死亡；警方击毙 17 名匪徒。</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>凯比州（Kebbi）</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>武装袭击 / 交火</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>不明武装匪帮（bandits）</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>不明武装匪帮（bandits）</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aljazeera.com/news/2026/8/11/dozens-killed-in-firefight-between-nigerian-armed-group-and-police</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 警察与小民；匪帮主动袭击警方属恐袭非反恐战果，故不落 N5。死亡只计受害方 12 人，不含被击毙的 17 名匪徒 [证据]At least 10 police officers, 17 'bandits' and two civilians have been killed in clashes with a group of armed  [日期]URL 内嵌 2026/8/11；正文『Police said on Tuesday』『The incident hap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FARC 分离派以路边『煤气罐炸弹』为诱饵伏击陆军车队，军人上前排爆时引爆。2 名军人死亡、10 余人受伤。</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>哥伦比亚</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>乌伊拉省 阿尔赫西拉斯（Algeciras）</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>路边炸弹伏击</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>FARC 分离派（Jorge Suárez Briceño 集团 Iván Díaz 支队）</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>FARC 分离派（Jorge Suárez Briceño 集团 Iván Díaz 支队）</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sociedadmedia.com/algeciras-huila-ambush-farc-dissidents-2026/</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[判据]P3 执行排爆任务的军人（当时非战斗状态）；以诱饵弹伏击属有组织武装暴力 [证据]FARC dissidents ambushed a Colombian Army convoy with explosives in rural Huila department on Wednesday, Augus [日期]正文明确『on Wednesday, August 12』；维基 Portal:Current events/2026 </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>不明枪手向正在执行抓捕任务的警察小队开火，2 名警员死亡。『自由者军』（Jamaat-ul-Ahrar，TTP 分支）宣称负责，称系为其成员被杀报复。</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>巴基斯坦</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>旁遮普省 拉合尔 巴达米巴格（Badami Bagh）</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>枪击</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>自由者军（Jamaat-ul-Ahrar，TTP 分支）</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>自由者军（Jamaat-ul-Ahrar，TTP 分支）</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aa.com.tr/en/asia-pacific/two-police-officers-killed-in-gun-attack-in-pakistan-s-lahore/4027016</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>P1b 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P1b 组织公开宣称（自由者军=Jamaat-ul-Ahrar，TTP 分支）；目标为执勤警员，P3 亦命中 [缺口]受伤数原文未给，按口径记 0，不等于「无人受伤」 [证据]Two police personnel were killed when unidentified gunmen opened fire on them in Pakistan's eastern city of La [日期]原文页头『14 August 2026』</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>巴达赫尚省省级行政首长（报道称 mayor）哈比卜·乌尔·拉赫曼·曼苏尔在车内遭爆炸身亡。为两周内该地区第二名遇袭身亡的塔利班高级官员。</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>阿富汗</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>巴达赫尚省 法扎巴德（Faizabad）</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>车载爆炸装置</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>未宣称</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>未宣称</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.washingtonpost.com/world/2026/08/14/afghanistan-explosion-mayor-killed/3ceeecea-97b3-11f1-9ef9-1be722184483_story.html</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 目标是塔利班政权省级行政首长——属「政府/国家象征」而非平民，仍在 P3 范围内。仅 1 死、无受伤数，数值偏弱故置信度 C。若评审方要求只计平民受害者，此条应移出 [缺口]受伤数原文未给，按口径记 0，不等于「无人受伤」 [证据]KABUL, Afghanistan — The mayor for Afghanistan's northeastern Badakhshan province has been killed in an explos [日期]URL 内嵌 /2026/08/14/（报道日）；正文『late on Thursday』，2026-08-13 为周四</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>袭击者逐户持砍刀杀害村民，妇孺占多数。地方议员称 23 人死亡、1 人后伤重不治；居民称至少 25 人。</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>高原州（Plateau）一村庄</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>武装袭击 / 砍刀屠杀</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>不明武装分子（农牧民冲突背景）</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>不明武装分子（农牧民冲突背景）</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/world/africa/least-25-killed-attack-nigerias-plateau-amid-reprisal-fears-2026-08-18/</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 逐户砍刀屠杀村民、妇孺为主；虽报道未点名组织，判据不要求主体识别（P3 本身不需组织名）。农牧冲突背景仅作诱因不作性质。此判可能被推翻 [缺口]受伤数原文未给，按口径记 0，不等于「无人受伤」 [证据]KANO,Nigeria, Aug 18 (Reuters) - At least 25 people were killed in an overnight attack on a village in Nigeria [日期]URL 内嵌 2026-08-18；原文首句『KANO,Nigeria, Aug 18 (Reuters)』；Al Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>分离主义叛乱分子在南部四府数十处同时实施协同纵火与爆炸，焚烧政府办公楼、商铺、便利店、车辆与电信塔、电线杆，3 名平民受伤。军方称为对镇压行动的报复。</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>伊图里省 Mambasa 地区</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>那拉提瓦、也拉、北大年、宋卡四府（含陶公府 Cho Airong 等）</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>协同纵火 / 爆炸</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>南部分离主义叛乱分子（主要为 BRN）</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>南部分离主义叛乱分子（主要为 BRN）</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aljazeera.com/news/2026/8/23/dozens-of-attacks-in-southern-thailand-wound-three-people</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 政府办公楼+商铺+电信塔，数十处协同纵火；3 平民伤达「受伤≥3」门槛，无死亡仍计入 [证据]Dozens of coordinated arson and incendiary attacks across Thailand's south left at least three people wounded  [日期]URL 内嵌 2026/8/23（报道日）；正文『51 attacks late on Saturday』，2026-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>武装帮派夜间突袭肯斯科夫社区，杀害至少 47 人、伤 22 人、绑架 50 余人，焚烧民居。为海地冲突中最大规模绑架事件之一。</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>海地</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>西部省 肯斯科夫（Kenscoff，太子港近郊）</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>帮派武装袭击 / 纵火 / 大规模绑架</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>海地武装帮派（未点名具体帮派）</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>海地武装帮派（未点名具体帮派）</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/world/2026/aug/25/gang-attack-kenscoff-port-au-prince-haiti</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 社区居民；武装帮派大规模杀人+绑架+纵火，属有组织武装暴力。帮派暴力计入恐袭是本库口径选择，见争议说明 [证据]At least 47 people were killed and more than 50 others kidnapped when armed men attacked a once peaceful commu [日期]URL 内嵌 /2026/aug/25/（报道日）；正文『Sunday's attack』，2026-08-23 为周日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>不明枪手伏击联合国南苏丹特派团（UNMISS）巡逻队，2 名埃塞俄比亚籍维和人员死亡，另有 3 名维和人员、2 名警察和 2 名平民受伤。</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>南苏丹</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>琼莱州（Jonglei）</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>伏击</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>不明枪手</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>不明枪手</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.africanews.com/2026/08/25/south-sudan-two-un-peacekeepers-killed-seven-injured/</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[判据]P3 联合国维和人员与警察（非战斗状态）+平民；不明枪手伏击 [证据]（维基 2026-08-24 条目）Two peacekeepers from Ethiopia of the United Nations Mission in South Sudan are killed in an [日期]URL 内嵌 2026/08/25（报道日）；维基 Portal:Current events/2026 August </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>疑似『民主同盟军』（ADF）周末袭击两座村庄，马巴库哈 10 人、阿马尼 11 人遇害，共 21 名平民死亡；医院、教堂与多栋民居被焚。此为滚动数字，初期报道称 7 死。</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>刚果（金）</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>伊图里省 曼巴萨地区 马巴库哈村（Mabakuha）、阿马尼村（Amani）</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>枪击</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>枪支</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>疑似 ADF（与伊斯兰国有关联的民兵）</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>ADF</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>武装袭击 / 纵火</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>民主同盟军（ADF，ISIS 关联）</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>民主同盟军（ADF，ISIS 关联）</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://www.aa.com.tr/en/africa/death-toll-from-rebel-attack-in-eastern-congo-rises-to-21/4042775</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>示例组</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>P3 平民村庄；反证 N1/N2 未成立</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>[证据] At least 10 people were killed in Mabakuha village, while 11 bodies were recovered in Amani village, all in Mambasa territory</t>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 平民村庄、医院、教堂；疑似 ADF（ISIS 关联，联合国名单）。事发日按原文「Friday and Saturday」定 8/28 [缺口]受伤数原文未给，按口径记 0，不等于「无人受伤」 [证据]The death toll from weekend attacks by suspected Allied Democratic Forces (ADF) rebels in villages in eastern  [日期]原文页头『31 August 2026』；正文『attacks took place Friday and Saturd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>一辆装有约 80 公斤炸药的被盗车辆在警察局旁引爆，1 名平民死亡、11 人受伤（含 2 名警员）。警方归因于『民族解放军』（ELN）。</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>哥伦比亚</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>北桑坦德省 洛斯帕蒂奥斯（Los Patios）警察局外</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>汽车炸弹（VBIED）</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>民族解放军（ELN）</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>民族解放军（ELN）</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.france24.com/en/live-news/20260901-car-bomb-at-colombian-police-station-kills-one-injures-11</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>第七组</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>P3 命中；反证已逐条排查</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>[判据]P3 警察局（国家象征）+平民；ELN 归因；1 死 11 伤 [证据]The attack on Monday in the department of Norte de Santander killed one civilian and injured eleven others, in [日期]原文『Issued on: 01/09/2026』（报道日）；正文『The attack on Monday』，2026</t>
         </is>
       </c>
     </row>
